--- a/data/trans_orig/P36BPD06_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD06_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de mantequilla, margarina o nata que consume al día en 2023</t>
+          <t>Población según el número de raciones de mantequilla, margarina o nata que consume al día en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117574</t>
+          <t>116456</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154726</t>
+          <t>154163</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>192617</t>
+          <t>194207</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>229879</t>
+          <t>232658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>323590</t>
+          <t>319534</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>374149</t>
+          <t>372118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>354445</t>
+          <t>355008</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>391597</t>
+          <t>392715</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>523590</t>
+          <t>520811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>560852</t>
+          <t>559262</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>888492</t>
+          <t>890523</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>939051</t>
+          <t>943107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,69%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>341498</t>
+          <t>358519</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>560978</t>
+          <t>566570</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>540411</t>
+          <t>544347</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1144952</t>
+          <t>1186458</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1001024</t>
+          <t>993483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1785790</t>
+          <t>1754901</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1723464</t>
+          <t>1717872</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1942944</t>
+          <t>1925923</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1090199</t>
+          <t>1048693</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1694740</t>
+          <t>1690804</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2733803</t>
+          <t>2764692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3518569</t>
+          <t>3526110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94993</t>
+          <t>94516</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144967</t>
+          <t>145269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98687</t>
+          <t>99603</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132478</t>
+          <t>133312</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206317</t>
+          <t>204733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>262866</t>
+          <t>262695</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>499045</t>
+          <t>498743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549019</t>
+          <t>549496</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>527985</t>
+          <t>527151</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>561776</t>
+          <t>560860</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1041609</t>
+          <t>1041780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1098158</t>
+          <t>1099742</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,31%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>555707</t>
+          <t>584396</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>820440</t>
+          <t>822194</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>864715</t>
+          <t>873857</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1612801</t>
+          <t>1536955</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,17 +1824,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1803122</t>
+          <t>1803123</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1578966</t>
+          <t>1591482</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2322108</t>
+          <t>2314766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2617186</t>
+          <t>2615432</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2881919</t>
+          <t>2853230</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2036282</t>
+          <t>2112128</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2784368</t>
+          <t>2775226</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5283587</t>
+          <t>5283586</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4764601</t>
+          <t>4771943</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5507743</t>
+          <t>5495227</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD06_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD06_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>134317</t>
+          <t>152540</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>134673</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154163</t>
+          <t>175888</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>211413</t>
+          <t>233722</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>194207</t>
+          <t>214796</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>232658</t>
+          <t>255215</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>345730</t>
+          <t>386261</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>319534</t>
+          <t>359233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>372118</t>
+          <t>417903</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>374854</t>
+          <t>419749</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355008</t>
+          <t>396401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>392715</t>
+          <t>437616</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>542056</t>
+          <t>586224</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>520811</t>
+          <t>564731</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>559262</t>
+          <t>605150</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>916911</t>
+          <t>1005974</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>890523</t>
+          <t>974332</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>943107</t>
+          <t>1033002</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>509171</t>
+          <t>572289</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>509171</t>
+          <t>572289</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>509171</t>
+          <t>572289</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>753469</t>
+          <t>819946</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>753469</t>
+          <t>819946</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753469</t>
+          <t>819946</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1262641</t>
+          <t>1392235</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1262641</t>
+          <t>1392235</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1262641</t>
+          <t>1392235</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>488203</t>
+          <t>568359</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>358519</t>
+          <t>521514</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>566570</t>
+          <t>617748</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>737851</t>
+          <t>544214</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>544347</t>
+          <t>507897</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1186458</t>
+          <t>587003</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1226054</t>
+          <t>1112572</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>993483</t>
+          <t>1055266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1754901</t>
+          <t>1178143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1796239</t>
+          <t>1656237</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1717872</t>
+          <t>1606848</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1925923</t>
+          <t>1703082</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1497300</t>
+          <t>1623325</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1048693</t>
+          <t>1580536</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1690804</t>
+          <t>1659642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3293539</t>
+          <t>3279563</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2764692</t>
+          <t>3213992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3526110</t>
+          <t>3336869</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2284442</t>
+          <t>2224596</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2284442</t>
+          <t>2224596</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2284442</t>
+          <t>2224596</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235151</t>
+          <t>2167539</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235151</t>
+          <t>2167539</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235151</t>
+          <t>2167539</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4519593</t>
+          <t>4392135</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4519593</t>
+          <t>4392135</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4519593</t>
+          <t>4392135</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>115773</t>
+          <t>121644</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94516</t>
+          <t>102878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145269</t>
+          <t>144789</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>115565</t>
+          <t>130210</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99603</t>
+          <t>113550</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133312</t>
+          <t>149709</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>231338</t>
+          <t>251854</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>204733</t>
+          <t>223789</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>262695</t>
+          <t>280816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>528239</t>
+          <t>587328</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>498743</t>
+          <t>564183</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549496</t>
+          <t>606094</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>544898</t>
+          <t>604667</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>527151</t>
+          <t>585168</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>560860</t>
+          <t>621327</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1073137</t>
+          <t>1191995</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1041780</t>
+          <t>1163033</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1099742</t>
+          <t>1220060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,5%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>644012</t>
+          <t>708972</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>644012</t>
+          <t>708972</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644012</t>
+          <t>708972</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1304475</t>
+          <t>1443849</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304475</t>
+          <t>1443849</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304475</t>
+          <t>1443849</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>738293</t>
+          <t>842542</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>584396</t>
+          <t>785225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>822194</t>
+          <t>896250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1064829</t>
+          <t>908146</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>873857</t>
+          <t>864608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1536955</t>
+          <t>959671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1803123</t>
+          <t>1750688</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1591482</t>
+          <t>1675763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2314766</t>
+          <t>1816120</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2699333</t>
+          <t>2663315</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2615432</t>
+          <t>2609607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2853230</t>
+          <t>2720632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2584254</t>
+          <t>2814216</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2112128</t>
+          <t>2762691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2775226</t>
+          <t>2857754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5283586</t>
+          <t>5477531</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4771943</t>
+          <t>5412099</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5495227</t>
+          <t>5552456</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3437626</t>
+          <t>3505857</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3437626</t>
+          <t>3505857</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3437626</t>
+          <t>3505857</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649083</t>
+          <t>3722362</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649083</t>
+          <t>3722362</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649083</t>
+          <t>3722362</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7086709</t>
+          <t>7228219</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7086709</t>
+          <t>7228219</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7086709</t>
+          <t>7228219</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
